--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcBillExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcBillExport.xlsx
@@ -27,11 +27,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>质检单号</t>
   </si>
   <si>
+    <t>来源单号</t>
+  </si>
+  <si>
+    <t>来源类型</t>
+  </si>
+  <si>
     <t>采购单号</t>
   </si>
   <si>
@@ -108,6 +114,12 @@
   </si>
   <si>
     <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.sourceTypeName}</t>
   </si>
   <si>
     <t>{.purchaseOrderCode}</t>
@@ -684,7 +696,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1375,23 +1387,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="6" width="30" customWidth="1"/>
-    <col min="7" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="1" max="8" width="30" customWidth="1"/>
+    <col min="9" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="30" customWidth="1"/>
-    <col min="18" max="19" width="20" customWidth="1"/>
-    <col min="20" max="20" width="30" customWidth="1"/>
-    <col min="21" max="22" width="20" customWidth="1"/>
-    <col min="23" max="26" width="30" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="14" max="18" width="20" customWidth="1"/>
+    <col min="19" max="19" width="30" customWidth="1"/>
+    <col min="20" max="21" width="20" customWidth="1"/>
+    <col min="22" max="22" width="30" customWidth="1"/>
+    <col min="23" max="24" width="20" customWidth="1"/>
+    <col min="25" max="28" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:26">
+    <row r="1" ht="15" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1470,85 +1482,97 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:28">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcBillExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcBillExport.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24945" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="质检单数据" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>质检单号</t>
   </si>
@@ -44,6 +44,9 @@
     <t>质检状态</t>
   </si>
   <si>
+    <t>作废状态</t>
+  </si>
+  <si>
     <t>质检员</t>
   </si>
   <si>
@@ -126,6 +129,9 @@
   </si>
   <si>
     <t>{.qcStatusName}</t>
+  </si>
+  <si>
+    <t>{.invalidStatusName}</t>
   </si>
   <si>
     <t>{.qcUserName}</t>
@@ -1387,23 +1393,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="8" width="30" customWidth="1"/>
-    <col min="9" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="30" customWidth="1"/>
-    <col min="14" max="18" width="20" customWidth="1"/>
-    <col min="19" max="19" width="30" customWidth="1"/>
-    <col min="20" max="21" width="20" customWidth="1"/>
-    <col min="22" max="22" width="30" customWidth="1"/>
-    <col min="23" max="24" width="20" customWidth="1"/>
-    <col min="25" max="28" width="30" customWidth="1"/>
+    <col min="1" max="9" width="30" customWidth="1"/>
+    <col min="10" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="15" max="19" width="20" customWidth="1"/>
+    <col min="20" max="20" width="30" customWidth="1"/>
+    <col min="21" max="22" width="20" customWidth="1"/>
+    <col min="23" max="23" width="30" customWidth="1"/>
+    <col min="24" max="25" width="20" customWidth="1"/>
+    <col min="26" max="29" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:28">
+    <row r="1" ht="15" spans="1:29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1488,91 +1494,97 @@
       <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:29">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcBillExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcBillExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24945" windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="质检单数据" sheetId="1" r:id="rId1"/>
@@ -71,16 +71,16 @@
     <t>SKU名称</t>
   </si>
   <si>
-    <t>总数量</t>
-  </si>
-  <si>
-    <t>质检量</t>
-  </si>
-  <si>
-    <t>质检合格量</t>
-  </si>
-  <si>
-    <t>质检不良量</t>
+    <t>送检数量</t>
+  </si>
+  <si>
+    <t>抽检数量</t>
+  </si>
+  <si>
+    <t>抽检良品数量</t>
+  </si>
+  <si>
+    <t>抽检不良品数量</t>
   </si>
   <si>
     <t>检验结果</t>
@@ -98,10 +98,10 @@
     <t>不良现象</t>
   </si>
   <si>
-    <t>质检合格率(%)</t>
-  </si>
-  <si>
-    <t>质检不良率(%)</t>
+    <t>抽检合格率(%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 抽检不合格率(%)</t>
   </si>
   <si>
     <t>仓库</t>
